--- a/data/trans_camb/IP11A_R-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP11A_R-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>0.4719073333124948</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-2.831874489961104</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2.266411332707312</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-3.695972628375221</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>1.194941650741258</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-3.228386327148121</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-5.891254540500558</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-19.94706033258048</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-7.42700154185105</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-15.64822570598229</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-5.066864820918175</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-9.984034563930324</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>10.29810402460976</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>20.26784181710256</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>10.70125358074518</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>0.1666413306752788</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.6132110706955219</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.3701358913252619</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -705,9 +710,6 @@
       <c r="F8" s="6" t="inlineStr"/>
       <c r="G8" s="6" t="inlineStr"/>
       <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -722,9 +724,6 @@
       <c r="F9" s="6" t="inlineStr"/>
       <c r="G9" s="6" t="inlineStr"/>
       <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +736,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-2.254972806232089</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-2.254972806232089</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>15.56698346675743</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>28.34202557242258</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>3.384263561018976</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>6.022148091841211</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +762,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-11.3295445313834</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-11.24017599849588</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-2.84400689461431</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-2.861081203451373</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +788,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>64.04613220373828</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>96.06383219298029</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>20.13607004838488</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>34.00155657703547</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +814,28 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>2.352468047677606</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>4.186113377107534</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -811,9 +850,6 @@
       <c r="F14" s="6" t="inlineStr"/>
       <c r="G14" s="6" t="inlineStr"/>
       <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -828,9 +864,6 @@
       <c r="F15" s="6" t="inlineStr"/>
       <c r="G15" s="6" t="inlineStr"/>
       <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +876,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>-10.01274701996618</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-10.01274701996618</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>31.34709696422412</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>11.59034525770364</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>1.613985539282406</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0.1053698061363614</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +902,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-43.26151016612498</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-44.16936252706762</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-10.69900635737266</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-10.80493718194075</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +928,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>48.28727375680517</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>21.38073907722727</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>16.77374641992531</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +954,28 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.3036254376957924</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.01982232971077171</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -917,9 +990,6 @@
       <c r="F20" s="6" t="inlineStr"/>
       <c r="G20" s="6" t="inlineStr"/>
       <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -934,9 +1004,6 @@
       <c r="F21" s="6" t="inlineStr"/>
       <c r="G21" s="6" t="inlineStr"/>
       <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1016,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>14.09371238644997</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>21.08037419574508</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>8.653546365710337</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>14.9882501256964</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1042,20 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="5" t="inlineStr"/>
       <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1064,20 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>59.31404790407672</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>61.11611817517855</v>
+      </c>
       <c r="E24" s="5" t="inlineStr"/>
       <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="n">
+        <v>37.24021906977962</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>43.31405388510341</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1086,28 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
       <c r="E25" s="6" t="inlineStr"/>
       <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1023,9 +1122,6 @@
       <c r="F26" s="6" t="inlineStr"/>
       <c r="G26" s="6" t="inlineStr"/>
       <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1040,9 +1136,6 @@
       <c r="F27" s="6" t="inlineStr"/>
       <c r="G27" s="6" t="inlineStr"/>
       <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1148,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-0.3234550865271101</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>3.430568462458064</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>7.834312720200125</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>6.35149341595236</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>2.726981825111678</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>4.637703836310894</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1174,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-6.339648702352141</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-3.681199024307898</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-1.462388185594576</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-1.716179260332891</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-1.633345751117108</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1200,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>5.956007402773468</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>20.32226190302326</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>21.23637707979252</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>22.13622712674718</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>8.695608387502613</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>14.52289173006199</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1226,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.0906899067329635</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0.9618582203847699</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>5.399587255452641</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>4.377594324699315</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>1.009489616750767</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>1.716811540586383</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1127,11 +1256,12 @@
       <c r="D32" s="6" t="inlineStr"/>
       <c r="E32" s="6" t="inlineStr"/>
       <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="G32" s="6" t="n">
+        <v>-0.8058812404926387</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1144,11 +1274,12 @@
       <c r="D33" s="6" t="inlineStr"/>
       <c r="E33" s="6" t="inlineStr"/>
       <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="G33" s="6" t="n">
+        <v>7.012823374223482</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>11.97239189408406</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1290,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
